--- a/review/review_ar_sy.xlsx
+++ b/review/review_ar_sy.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,13 +34,22 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -60,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -71,13 +80,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -445,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -558,30 +573,30 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>• Rows marked 🌍 name the asker's nationality. Check that this sounds right.</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>• IMPORTANT: Mixing in German words (Ausbildung, Anmeldung) is fine if people really do that. But if there is an expression in your language, use it preferably.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>• Everyday wording is better than formal or legal wording.</t>
+          <t>• Rows marked 🌍 name the asker's nationality. Check that this sounds right.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>• These questions are written in Syrian (Levantine) colloquial Arabic on purpose, the way people type in a chat. Correct them to how you would actually write it; any Syrian city's dialect is fine.</t>
+          <t>• Everyday wording is better than formal or legal wording.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>• Mixing in German words (Ausbildung, Duldung) is fine if people really do that.</t>
+          <t>• These questions are written in Syrian (Levantine) colloquial Arabic on purpose, the way people type in a chat. Correct them to how you would actually write it; any Syrian city's dialect is fine.</t>
         </is>
       </c>
     </row>
@@ -613,16 +628,23 @@
       <c r="A27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>هالجمل مسودة أولى كتبها نموذج ذكاء اصطناعي (Claude Opus 5.5)، وممكن يكون فيها غلطات أو حكي مو طبيعي، فصحّحها براحتك متل ما بتكتبها إنت.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>ملخص: هالأسئلة مكتوبة باللهجة السورية عن قصد، متل ما الناس بتكتب بالشات. إذا السؤال طبيعي، اختار ✓ بعمود OK?. إذا مو طبيعي، اكتب كيف كنت رح تكتبه بعمود Correction. ما تغيّر المعنى. عمود الفصحى للمرجع بس. شكراً!</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>مهم: عادي تستخدم كلمات ألمانية (متل Ausbildung أو Anmeldung) إذا الناس فعلاً بيحكوها هيك، بس إذا في كلمة بالعربي، الأحسن تستخدمها.</t>
         </is>
       </c>
     </row>
@@ -651,42 +673,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Syrian Arabic</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>MSA (reference only)</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>OK?</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -706,18 +728,18 @@
           <t>🌍 I'm American. Once I finish my master's degree in Germany, can I get a work visa?</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>أنا أمريكاني. إذا خلّصت الماستر بألمانيا، فيني آخد فيزا شغل؟</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>أنا أمريكي. هل يمكنني الحصول على تأشيرة عمل بعد أن أنهي الماجستير في ألمانيا؟</t>
         </is>
       </c>
       <c r="F2" s="2" t="n"/>
-      <c r="G2" s="5" t="n"/>
+      <c r="G2" s="6" t="n"/>
       <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
@@ -734,18 +756,18 @@
           <t>🌍 What do Nigerian citizens have to do to work in Germany?</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>النيجيريين شو لازم يعملوا لحتى يشتغلوا بألمانيا؟</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>ما الذي يجب على المواطنين النيجيريين فعله للعمل في ألمانيا؟</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="5" t="n"/>
+      <c r="G3" s="6" t="n"/>
       <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
@@ -762,18 +784,18 @@
           <t>🌍 I'm moving from Italy to Germany. Do I have to do the Anmeldung?</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>عم انتقل من إيطاليا لألمانيا. لازم سجّل السكن؟</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>سأنتقل من إيطاليا إلى ألمانيا. هل يجب أن أقوم بتسجيل السكن؟</t>
         </is>
       </c>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="5" t="n"/>
+      <c r="G4" s="6" t="n"/>
       <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
@@ -790,18 +812,18 @@
           <t>🌍 Can Polish citizens live in Germany without a visa and without doing the Anmeldung?</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>البولنديين فيهن يعيشوا بألمانيا بلا فيزا وبلا تسجيل سكن؟</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>هل يمكن للمواطنين البولنديين العيش في ألمانيا دون تأشيرة ودون تسجيل السكن؟</t>
         </is>
       </c>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="5" t="n"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
@@ -818,18 +840,18 @@
           <t>🌍 I'm Syrian and I'm here as a refugee. What money can I receive?</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>أنا سوري وجاي لاجئ. شو المصاري اللي فيني آخدها؟</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>أنا سوري وموجود هنا كلاجئ. ما المساعدات المالية التي يمكنني الحصول عليها؟</t>
         </is>
       </c>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="5" t="n"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
@@ -846,18 +868,18 @@
           <t>🌍 I'm coming to Germany from India. Do I need a visa?</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>جاي على ألمانيا من الهند. بحتاج فيزا؟</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>سأدخل ألمانيا قادماً من الهند. هل أحتاج إلى تأشيرة؟</t>
         </is>
       </c>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
@@ -874,18 +896,18 @@
           <t>🌍 Can someone with dual citizenship get permanent residence in Germany? The countries are Brazil and Australia.</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>اللي معه جنسيتين فيه ياخد إقامة دائمة بألمانيا؟ الجنسيتين برازيلية وأسترالية.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>هل يمكن لمزدوجي الجنسية الحصول على الإقامة الدائمة في ألمانيا؟ الجنسيتان هما البرازيلية والأسترالية.</t>
         </is>
       </c>
       <c r="F8" s="2" t="n"/>
-      <c r="G8" s="5" t="n"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
@@ -902,18 +924,18 @@
           <t>Citizens of which countries can enter Germany without a visa and stay for more than two months?</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>شو الجنسيات اللي بيقدر أصحابها يفوتوا على ألمانيا بلا فيزا ويضلّوا أكتر من شهرين؟</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>ما الجنسيات التي يمكن لأصحابها دخول ألمانيا دون تأشيرة والبقاء فيها أكثر من شهرين؟</t>
         </is>
       </c>
       <c r="F9" s="2" t="n"/>
-      <c r="G9" s="5" t="n"/>
+      <c r="G9" s="6" t="n"/>
       <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
@@ -930,18 +952,18 @@
           <t>Does Germany have a visa for freelancers?</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>في بألمانيا فيزا للفريلانسر؟</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>هل يوجد في ألمانيا تأشيرة خاصة بالعمل الحر (الفريلانسر)؟</t>
         </is>
       </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
@@ -958,18 +980,18 @@
           <t>Can people from non-EU countries also join the artists' social insurance?</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>الناس اللي من برّا الاتحاد الأوروبي فيهن كمان يشتركوا بالتأمين الاجتماعي للفنانين؟</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>هل يمكن للأشخاص من دول خارج الاتحاد الأوروبي أيضاً الانضمام إلى التأمين الاجتماعي للفنانين؟</t>
         </is>
       </c>
       <c r="F11" s="2" t="n"/>
-      <c r="G11" s="5" t="n"/>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
@@ -986,18 +1008,18 @@
           <t>After graduating I got the 18-month job-seeker residence permit. If I don't find a job within 18 months, do I have to leave Germany? Can it be extended?</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>بعد ما اتخرجت أخدت إقامة البحث عن شغل لـ18 شهر. إذا ما لقيت شغل خلال الـ18 شهر، لازم اطلع من ألمانيا؟ بتتمدّد؟</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>بعد التخرج حصلت على تصريح إقامة للبحث عن عمل لمدة 18 شهراً. إذا لم أجد عملاً خلال 18 شهراً، فهل يجب أن أغادر ألمانيا؟ وهل يمكن تمديده؟</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
-      <c r="G12" s="5" t="n"/>
+      <c r="G12" s="6" t="n"/>
       <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
@@ -1014,18 +1036,18 @@
           <t>🌍 I'm South Korean and stayed in Germany visa-free for two and a half months. If I go back home and then come back, can I stay again for less than three months?</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>أنا كوري جنوبي وقعدت بألمانيا شهرين ونص بلا فيزا. إذا رجعت على بلدي ورجعت، فيني اقعد كمان مرة أقل من تلت شهور؟</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>أنا كوري جنوبي وبقيت في ألمانيا شهرين ونصفاً دون تأشيرة. إذا عدت إلى بلدي ثم رجعت، فهل يمكنني البقاء مرة أخرى أقل من ثلاثة أشهر؟</t>
         </is>
       </c>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="5" t="n"/>
+      <c r="G13" s="6" t="n"/>
       <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
@@ -1042,18 +1064,18 @@
           <t>Can non-EU students work in Germany while they study? How much are they allowed to work?</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>الطلاب الأجانب اللي من برّا الاتحاد الأوروبي فيهن يشتغلوا بألمانيا وهنن عم يدرسوا؟ وقديش مسموحلهن يشتغلوا؟</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>هل يمكن للطلاب الأجانب من خارج الاتحاد الأوروبي العمل في ألمانيا أثناء دراستهم؟ وما مقدار العمل المسموح لهم به؟</t>
         </is>
       </c>
       <c r="F14" s="2" t="n"/>
-      <c r="G14" s="5" t="n"/>
+      <c r="G14" s="6" t="n"/>
       <c r="H14" s="2" t="n"/>
     </row>
     <row r="15">
@@ -1070,18 +1092,18 @@
           <t>🌍 I'm Mexican. If I get German citizenship, do I have to give up my Mexican citizenship?</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>أنا مكسيكي. إذا أخدت الجنسية الألمانية، لازم اتنازل عن الجنسية المكسيكية؟</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>أنا مكسيكي. إذا حصلت على الجنسية الألمانية، فهل يجب أن أتخلى عن جنسيتي المكسيكية؟</t>
         </is>
       </c>
       <c r="F15" s="2" t="n"/>
-      <c r="G15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
       <c r="H15" s="2" t="n"/>
     </row>
     <row r="16">
@@ -1098,18 +1120,18 @@
           <t>How many years do I have to live in Germany before I can get an EU Blue Card?</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>قديش سنة لازم عيش بألمانيا لحتى آخد البطاقة الزرقاء؟</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>كم سنة يجب أن أعيش في ألمانيا قبل أن أتمكن من الحصول على البطاقة الزرقاء؟</t>
         </is>
       </c>
       <c r="F16" s="2" t="n"/>
-      <c r="G16" s="5" t="n"/>
+      <c r="G16" s="6" t="n"/>
       <c r="H16" s="2" t="n"/>
     </row>
     <row r="17">
@@ -1126,18 +1148,18 @@
           <t>🌍 I'm Vietnamese. What residence permit do I need to do an Ausbildung in Germany, and what are the conditions?</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>أنا فيتنامي. شو نوع الإقامة اللي بحتاجها لحتى أعمل أوسبيلدونغ بألمانيا، وشو الشروط؟</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>أنا فيتنامي. ما تصريح الإقامة الذي أحتاجه لعمل أوسبيلدونغ في ألمانيا، وما شروطه؟</t>
         </is>
       </c>
       <c r="F17" s="2" t="n"/>
-      <c r="G17" s="5" t="n"/>
+      <c r="G17" s="6" t="n"/>
       <c r="H17" s="2" t="n"/>
     </row>
     <row r="18">
@@ -1154,18 +1176,18 @@
           <t>How long after getting an EU Blue Card can I get a permanent settlement permit?</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>بعد ما آخد البطاقة الزرقاء، قديش لازم استنى لحتى آخد الإقامة الدائمة؟</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>بعد كم من الوقت من حصولي على البطاقة الزرقاء يمكنني الحصول على الإقامة الدائمة؟</t>
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="5" t="n"/>
+      <c r="G18" s="6" t="n"/>
       <c r="H18" s="2" t="n"/>
     </row>
     <row r="19">
@@ -1182,18 +1204,18 @@
           <t>I don't have a university degree, only work experience in IT. Can I get an EU Blue Card?</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>ما معي شهادة جامعية، بس عندي خبرة بشغل الآي تي. فيني آخد البطاقة الزرقاء؟</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>ليست لدي شهادة جامعية، بل خبرة عملية في مجال تكنولوجيا المعلومات فقط. هل يمكنني الحصول على البطاقة الزرقاء الأوروبية؟</t>
         </is>
       </c>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="5" t="n"/>
+      <c r="G19" s="6" t="n"/>
       <c r="H19" s="2" t="n"/>
     </row>
     <row r="20">
@@ -1210,18 +1232,18 @@
           <t>Can I have a side job while I'm doing my Ausbildung?</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>فيني اشتغل شغلة جانبية وأنا عم أعمل الأوسبيلدونغ؟</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>هل يمكنني العمل في وظيفة جانبية أثناء الأوسبيلدونغ؟</t>
         </is>
       </c>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="5" t="n"/>
+      <c r="G20" s="6" t="n"/>
       <c r="H20" s="2" t="n"/>
     </row>
     <row r="21">
@@ -1238,18 +1260,18 @@
           <t>If a German company wants to bring in a foreign employee quickly, is there a way to speed up the process?</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>إذا شركة ألمانية بدها تجيب موظف أجنبي بسرعة، في طريقة تسرّع المعاملة؟</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>إذا أرادت شركة ألمانية استقدام موظف أجنبي بسرعة، فهل هناك طريقة لتسريع الإجراءات؟</t>
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="5" t="n"/>
+      <c r="G21" s="6" t="n"/>
       <c r="H21" s="2" t="n"/>
     </row>
     <row r="22">
@@ -1266,18 +1288,18 @@
           <t>If I'm working on an employment residence permit and quit my job earlier than planned, do I have to tell the immigration office?</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>إذا أنا شغال بإقامة عمل وتركت الشغل قبل الوقت المتفق عليه، لازم خبّر دائرة الأجانب؟</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>إذا كنت أعمل بتصريح إقامة لغرض العمل وتركت وظيفتي قبل الموعد المخطط له، فهل يجب أن أبلغ دائرة الأجانب؟</t>
         </is>
       </c>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="5" t="n"/>
+      <c r="G22" s="6" t="n"/>
       <c r="H22" s="2" t="n"/>
     </row>
     <row r="23">
@@ -1294,18 +1316,18 @@
           <t>What conditions do I have to meet to get a regular settlement permit without a Blue Card?</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>شو الشروط اللي لازم تكون عندي لحتى آخد إقامة دائمة عادية بدون البطاقة الزرقاء؟</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>ما الشروط التي يجب أن أستوفيها للحصول على تصريح إقامة دائمة عادي دون البطاقة الزرقاء؟</t>
         </is>
       </c>
       <c r="F23" s="2" t="n"/>
-      <c r="G23" s="5" t="n"/>
+      <c r="G23" s="6" t="n"/>
       <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
@@ -1322,18 +1344,18 @@
           <t>🌍 I'm a student from Kenya. Do I have to join the public health insurance in Germany?</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>أنا طالب من كينيا. لازم اشترك بالتأمين الصحي الحكومي بألمانيا؟</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>أنا طالب من كينيا. هل يجب عليّ الاشتراك في التأمين الصحي الحكومي في ألمانيا؟</t>
         </is>
       </c>
       <c r="F24" s="2" t="n"/>
-      <c r="G24" s="5" t="n"/>
+      <c r="G24" s="6" t="n"/>
       <c r="H24" s="2" t="n"/>
     </row>
     <row r="25">
@@ -1350,18 +1372,18 @@
           <t>🌍 I'm from Colombia. What are the requirements for working as an au pair in Germany?</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>أنا من كولومبيا. شو الشروط لحتى اشتغل أوبير بألمانيا؟</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>أنا من كولومبيا. ما شروط العمل كأوبير في ألمانيا؟</t>
         </is>
       </c>
       <c r="F25" s="2" t="n"/>
-      <c r="G25" s="5" t="n"/>
+      <c r="G25" s="6" t="n"/>
       <c r="H25" s="2" t="n"/>
     </row>
     <row r="26">
@@ -1378,18 +1400,18 @@
           <t>I'm still enrolled at university but I've found a full-time job. Can I switch to a work residence permit before I graduate?</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>أنا لسا مسجّل بالجامعة بس لقيت شغل دوام كامل. فيني حوّل لإقامة عمل قبل ما اتخرج؟</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>ما زلت مسجلاً في الجامعة لكنني وجدت وظيفة بدوام كامل. هل يمكنني التحول إلى تصريح إقامة لغرض العمل قبل التخرج؟</t>
         </is>
       </c>
       <c r="F26" s="2" t="n"/>
-      <c r="G26" s="5" t="n"/>
+      <c r="G26" s="6" t="n"/>
       <c r="H26" s="2" t="n"/>
     </row>
     <row r="27">
@@ -1406,18 +1428,18 @@
           <t>What conditions do I need to meet to get an Opportunity Card?</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>شو الشروط اللي لازم تكون عندي لحتى آخد بطاقة الفرص؟</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>ما الشروط التي يجب أن أستوفيها للحصول على بطاقة الفرص؟</t>
         </is>
       </c>
       <c r="F27" s="2" t="n"/>
-      <c r="G27" s="5" t="n"/>
+      <c r="G27" s="6" t="n"/>
       <c r="H27" s="2" t="n"/>
     </row>
     <row r="28">
@@ -1434,18 +1456,18 @@
           <t>🌍 Can South Korean citizens get a work visa for Germany without a university degree?</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>الكوريين الجنوبيين فيهن ياخدوا فيزا شغل لألمانيا بدون شهادة جامعية؟</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>هل يمكن للمواطنين الكوريين الجنوبيين الحصول على تأشيرة عمل في ألمانيا دون شهادة جامعية؟</t>
         </is>
       </c>
       <c r="F28" s="2" t="n"/>
-      <c r="G28" s="5" t="n"/>
+      <c r="G28" s="6" t="n"/>
       <c r="H28" s="2" t="n"/>
     </row>
     <row r="29">
@@ -1462,18 +1484,18 @@
           <t>What does someone who completed vocational training abroad need to get a work residence permit in Germany?</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>واحد خلّص تدريب مهني برّا، شو بيحتاج لحتى ياخد إقامة عمل بألمانيا؟</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>ما الذي يحتاجه شخص أكمل تدريبه المهني في الخارج للحصول على تصريح إقامة لغرض العمل في ألمانيا؟</t>
         </is>
       </c>
       <c r="F29" s="2" t="n"/>
-      <c r="G29" s="5" t="n"/>
+      <c r="G29" s="6" t="n"/>
       <c r="H29" s="2" t="n"/>
     </row>
     <row r="30">
@@ -1490,18 +1512,18 @@
           <t>🌍 I'm Austrian and live in Germany. When I move back home, do I have to do the Abmeldung?</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>أنا نمساوي وعايش بألمانيا. لما ارجع على بلدي، لازم الغي تسجيل السكن؟</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>أنا نمساوي وأعيش في ألمانيا. عندما أعود إلى بلدي، هل يجب أن ألغي تسجيل السكن؟</t>
         </is>
       </c>
       <c r="F30" s="2" t="n"/>
-      <c r="G30" s="5" t="n"/>
+      <c r="G30" s="6" t="n"/>
       <c r="H30" s="2" t="n"/>
     </row>
     <row r="31">
@@ -1518,18 +1540,18 @@
           <t>🌍 I'm Serbian. I have no degree and no qualification recognised in Germany, but long practical work experience. Can I work in Germany?</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>أنا صربي. ما معي شهادة ولا مؤهل معترف فيه بألمانيا، بس عندي خبرة عملية طويلة. فيني اشتغل بألمانيا؟</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>أنا صربي. ليست لدي شهادة ولا مؤهل معترف به في ألمانيا، لكن لدي خبرة عملية طويلة. هل يمكنني العمل في ألمانيا؟</t>
         </is>
       </c>
       <c r="F31" s="2" t="n"/>
-      <c r="G31" s="5" t="n"/>
+      <c r="G31" s="6" t="n"/>
       <c r="H31" s="2" t="n"/>
     </row>
     <row r="32">
@@ -1546,18 +1568,18 @@
           <t>If I work on a regular skilled-worker residence permit rather than a Blue Card, after how many years can I get a settlement permit?</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>إذا اشتغلت بإقامة عمالة ماهرة عادية مو بالبطاقة الزرقاء، بعد قديش سنة فيني آخد الإقامة الدائمة؟</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>إذا عملت بتصريح إقامة عادي للعمالة الماهرة بدلاً من البطاقة الزرقاء، فبعد كم سنة يمكنني الحصول على تصريح الإقامة الدائمة؟</t>
         </is>
       </c>
       <c r="F32" s="2" t="n"/>
-      <c r="G32" s="5" t="n"/>
+      <c r="G32" s="6" t="n"/>
       <c r="H32" s="2" t="n"/>
     </row>
     <row r="33">
@@ -1574,18 +1596,18 @@
           <t>What does the Federal Employment Agency check when a company hires a foreign worker?</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>شو بتفحص وكالة العمل الاتحادية لما شركة توظّف عامل أجنبي؟</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>ما الذي تفحصه الوكالة الاتحادية للعمل عندما توظف شركة عاملاً أجنبياً؟</t>
         </is>
       </c>
       <c r="F33" s="2" t="n"/>
-      <c r="G33" s="5" t="n"/>
+      <c r="G33" s="6" t="n"/>
       <c r="H33" s="2" t="n"/>
     </row>
     <row r="34">
@@ -1602,18 +1624,18 @@
           <t>🌍 I'm a nurse from the Philippines, and my qualification was only partly recognised in Germany. Can I stay and work in Germany while I make up for what's missing?</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>أنا ممرض من الفلبين، وشهادتي انعترف فيها بألمانيا بس جزئياً. فيني ضل واشتغل بألمانيا لحتى كمّل اللي ناقصني؟</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>أنا ممرض من الفلبين، واعتُرف بمؤهلي في ألمانيا اعترافاً جزئياً فقط. هل يمكنني البقاء والعمل في ألمانيا ريثما أستكمل ما ينقصني؟</t>
         </is>
       </c>
       <c r="F34" s="2" t="n"/>
-      <c r="G34" s="5" t="n"/>
+      <c r="G34" s="6" t="n"/>
       <c r="H34" s="2" t="n"/>
     </row>
     <row r="35">
@@ -1630,18 +1652,18 @@
           <t>Even if I meet all the requirements, on what grounds can a work residence permit still be refused?</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>حتى لو كل الشروط عندي، شو الأسباب اللي ممكن يرفضولي فيها إقامة العمل؟</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>حتى لو استوفيت جميع الشروط، ما الأسباب التي قد يُرفض بسببها تصريح الإقامة لغرض العمل؟</t>
         </is>
       </c>
       <c r="F35" s="2" t="n"/>
-      <c r="G35" s="5" t="n"/>
+      <c r="G35" s="6" t="n"/>
       <c r="H35" s="2" t="n"/>
     </row>
     <row r="36">
@@ -1658,18 +1680,18 @@
           <t>🌍 Can a Turkish citizen come to Germany for a seasonal job that lasts only a few months, like a farm harvest?</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>فيه واحد تركي يجي على ألمانيا لشغل موسمي كم شهر بس، متل قطاف المحاصيل بالمزارع؟</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>هل يمكن لمواطن تركي القدوم إلى ألمانيا من أجل عمل موسمي يستمر بضعة أشهر فقط، مثل حصاد المزارع؟</t>
         </is>
       </c>
       <c r="F36" s="2" t="n"/>
-      <c r="G36" s="5" t="n"/>
+      <c r="G36" s="6" t="n"/>
       <c r="H36" s="2" t="n"/>
     </row>
     <row r="37">
@@ -1686,18 +1708,18 @@
           <t>🌍 I'm Portuguese and work at the head office of a Spanish company. If I'm transferred to the German branch, what residence permit do I need?</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>أنا برتغالي وبشتغل بالمقر الرئيسي لشركة إسبانية. إذا نقلوني لفرع الشركة بألمانيا، شو الإقامة اللي لازم آخدها؟</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>أنا برتغالي وأعمل في المقر الرئيسي لشركة إسبانية. إذا نُقلت إلى فرع الشركة في ألمانيا، فما تصريح الإقامة الذي يجب أن أحصل عليه؟</t>
         </is>
       </c>
       <c r="F37" s="2" t="n"/>
-      <c r="G37" s="5" t="n"/>
+      <c r="G37" s="6" t="n"/>
       <c r="H37" s="2" t="n"/>
     </row>
     <row r="38">
@@ -1714,18 +1736,18 @@
           <t>Whether they are EU or non-EU citizens, do people in Germany have to pay social insurance or pension insurance contributions?</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>سواء كانوا من الاتحاد الأوروبي أو من برّاه، لازم يدفعوا تأمينات اجتماعية أو تأمين تقاعد بألمانيا؟</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>سواء كانوا مواطنين من الاتحاد الأوروبي أو من خارجه، هل يجب على الناس في ألمانيا دفع اشتراكات التأمين الاجتماعي أو تأمين التقاعد؟</t>
         </is>
       </c>
       <c r="F38" s="2" t="n"/>
-      <c r="G38" s="5" t="n"/>
+      <c r="G38" s="6" t="n"/>
       <c r="H38" s="2" t="n"/>
     </row>
     <row r="39">
@@ -1742,18 +1764,18 @@
           <t>Do EU citizens who move to Germany not have to do their Anmeldung?</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>مواطنين الاتحاد الأوروبي اللي بينتقلوا لألمانيا ما لازم يسجّلوا السكن؟</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>أليس على مواطني الاتحاد الأوروبي الذين ينتقلون إلى ألمانيا تسجيل السكن؟</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
-      <c r="G39" s="5" t="n"/>
+      <c r="G39" s="6" t="n"/>
       <c r="H39" s="2" t="n"/>
     </row>
     <row r="40">
@@ -1770,18 +1792,18 @@
           <t>🌍 I'm a Syrian citizen and applied for the October semester, but I haven't heard back yet. The semester starts in a month. Will I be able to get a visa?</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>أنا سوري وقدّمت على الفصل اللي بيبلّش بأكتوبر، بس لسا ما إجاني رد. الفصل بيبلّش بعد شهر. رح أقدر آخد فيزا؟</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>أنا مواطن سوري وتقدمت للفصل الدراسي الذي يبدأ في أكتوبر، لكنني لم أتلقَّ رداً بعد. يبدأ الفصل بعد شهر. هل سأتمكن من الحصول على تأشيرة؟</t>
         </is>
       </c>
       <c r="F40" s="2" t="n"/>
-      <c r="G40" s="5" t="n"/>
+      <c r="G40" s="6" t="n"/>
       <c r="H40" s="2" t="n"/>
     </row>
     <row r="41">
@@ -1798,18 +1820,18 @@
           <t>How many years do I have to live in Germany before I can get German citizenship?</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>قديش سنة لازم عيش بألمانيا لحتى آخد الجنسية الألمانية؟</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>كم سنة يجب أن أعيش في ألمانيا قبل أن أتمكن من الحصول على الجنسية الألمانية؟</t>
         </is>
       </c>
       <c r="F41" s="2" t="n"/>
-      <c r="G41" s="5" t="n"/>
+      <c r="G41" s="6" t="n"/>
       <c r="H41" s="2" t="n"/>
     </row>
     <row r="42">
@@ -1826,18 +1848,18 @@
           <t>🌍 I'm 32, Chinese, and have a bachelor's degree in computer science. I've been offered a salary of 48,000 euros. Will I get a Blue Card?</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>عمري 32 سنة، وأنا صيني، ومعي بكالوريوس هندسة كمبيوتر. إجاني عرض براتب 48,000 يورو. رح آخد البطاقة الزرقاء؟</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>عمري 32 عاماً، وأنا صيني، وأحمل درجة البكالوريوس في هندسة الحاسوب. تلقيت عرضاً براتب 48,000 يورو. هل سأحصل على البطاقة الزرقاء؟</t>
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
-      <c r="G42" s="5" t="n"/>
+      <c r="G42" s="6" t="n"/>
       <c r="H42" s="2" t="n"/>
     </row>
     <row r="43">
@@ -1854,18 +1876,18 @@
           <t>🌍 I'm Japanese, and the immigration office refused to extend my work residence permit. Is that decision unlawful? Would I win if I sued?</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>أنا ياباني، ودائرة الأجانب رفضت تمدّدلي إقامة العمل. هالقرار مخالف للقانون؟ إذا رفعت دعوى رح اربح؟</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>أنا ياباني، ورفضت دائرة الأجانب تمديد تصريح إقامتي لغرض العمل. هل هذا القرار غير قانوني؟ هل سأكسب القضية إذا رفعت دعوى؟</t>
         </is>
       </c>
       <c r="F43" s="2" t="n"/>
-      <c r="G43" s="5" t="n"/>
+      <c r="G43" s="6" t="n"/>
       <c r="H43" s="2" t="n"/>
     </row>
     <row r="44">
@@ -1882,18 +1904,18 @@
           <t>Can I work as a freelancer in Germany? If so, do I have to register somewhere first?</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>فيني اشتغل فريلانسر بألمانيا؟ وإذا فيني، لازم سجّل بمكان قبل؟</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>هل يمكنني العمل كفريلانسر في ألمانيا؟ وإذا كان ذلك ممكناً، هل يجب أن أسجل في مكان ما أولاً؟</t>
         </is>
       </c>
       <c r="F44" s="2" t="n"/>
-      <c r="G44" s="5" t="n"/>
+      <c r="G44" s="6" t="n"/>
       <c r="H44" s="2" t="n"/>
     </row>
     <row r="45">
@@ -1910,18 +1932,18 @@
           <t>Do Werkstudents and HiWis have to pay into the pension insurance? Or does the company or university take care of it?</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>الـ Werkstudent والـ HiWi لازم يدفعوا تأمين التقاعد؟ ولا الشركة أو الجامعة بتتكفّل بهالشي؟</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>هل يجب على طلاب الـ Werkstudent والـ HiWi دفع اشتراكات تأمين التقاعد؟ أم أن الشركة أو الجامعة تتولى ذلك؟</t>
         </is>
       </c>
       <c r="F45" s="2" t="n"/>
-      <c r="G45" s="5" t="n"/>
+      <c r="G45" s="6" t="n"/>
       <c r="H45" s="2" t="n"/>
     </row>
     <row r="46">
@@ -1938,18 +1960,18 @@
           <t>Can I get back the taxes I paid when I go back home?</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>الضرايب اللي دفعتها، فيني رجّعها لما ارجع على بلدي؟</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>هل يمكنني استرداد الضرائب التي دفعتها عند عودتي إلى بلدي؟</t>
         </is>
       </c>
       <c r="F46" s="2" t="n"/>
-      <c r="G46" s="5" t="n"/>
+      <c r="G46" s="6" t="n"/>
       <c r="H46" s="2" t="n"/>
     </row>
     <row r="47">
@@ -1966,18 +1988,18 @@
           <t>🌍 I'm Spanish. How many months do I have to live in Germany before I have to pay tax here?</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>أنا إسباني. قديش شهر لازم عيش بألمانيا لحتى يصير عليّ ادفع ضرايب هون؟</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>أنا إسباني. كم شهراً يجب أن أعيش في ألمانيا حتى يصبح عليّ دفع الضرائب فيها؟</t>
         </is>
       </c>
       <c r="F47" s="2" t="n"/>
-      <c r="G47" s="5" t="n"/>
+      <c r="G47" s="6" t="n"/>
       <c r="H47" s="2" t="n"/>
     </row>
     <row r="48">
@@ -1994,18 +2016,18 @@
           <t>🌍 My spouse lives in Canada. Can we be taxed jointly in Germany?</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>مرتي أو جوزي عايش بكندا. فينا نعمل تقييم ضريبي مشترك بألمانيا؟</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>زوجتي أو زوجي يعيش في كندا. هل يمكننا الخضوع للتقييم الضريبي المشترك في ألمانيا؟</t>
         </is>
       </c>
       <c r="F48" s="2" t="n"/>
-      <c r="G48" s="5" t="n"/>
+      <c r="G48" s="6" t="n"/>
       <c r="H48" s="2" t="n"/>
     </row>
     <row r="49">
@@ -2022,18 +2044,18 @@
           <t>🌍 I'm a South African citizen. Can I get Kindergeld in Germany?</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>أنا من جنوب أفريقيا. فيني آخد الكيندرغيلد بألمانيا؟</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>أنا مواطن من جنوب أفريقيا. هل يمكنني الحصول على الكيندرغيلد في ألمانيا؟</t>
         </is>
       </c>
       <c r="F49" s="2" t="n"/>
-      <c r="G49" s="5" t="n"/>
+      <c r="G49" s="6" t="n"/>
       <c r="H49" s="2" t="n"/>
     </row>
     <row r="50">
@@ -2050,18 +2072,18 @@
           <t>I also have income in Korea. Do I have to pay tax on it in both countries?</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>عندي دخل بكوريا الجنوبية كمان. لازم ادفع عليه ضرايب بالبلدين؟</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>لدي دخل في كوريا الجنوبية أيضاً. هل يجب أن أدفع الضرائب عليه في البلدين؟</t>
         </is>
       </c>
       <c r="F50" s="2" t="n"/>
-      <c r="G50" s="5" t="n"/>
+      <c r="G50" s="6" t="n"/>
       <c r="H50" s="2" t="n"/>
     </row>
     <row r="51">
@@ -2078,18 +2100,18 @@
           <t>When I first come to Germany, how do I get a Steuer-ID?</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>لما إجي على ألمانيا أول مرة، كيف باخد الرقم الضريبي؟</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>عندما أصل إلى ألمانيا لأول مرة، كيف أحصل على الرقم الضريبي؟</t>
         </is>
       </c>
       <c r="F51" s="2" t="n"/>
-      <c r="G51" s="5" t="n"/>
+      <c r="G51" s="6" t="n"/>
       <c r="H51" s="2" t="n"/>
     </row>
     <row r="52">
@@ -2106,18 +2128,18 @@
           <t>Is the money I earn from a Minijob taxed?</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>المصاري اللي بطلّعها من الميني جوب عليها ضرايب؟</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>هل تُفرض ضريبة على المال الذي أكسبه من الميني جوب؟</t>
         </is>
       </c>
       <c r="F52" s="2" t="n"/>
-      <c r="G52" s="5" t="n"/>
+      <c r="G52" s="6" t="n"/>
       <c r="H52" s="2" t="n"/>
     </row>
     <row r="53">
@@ -2134,18 +2156,18 @@
           <t>If I don't pay into the pension insurance, can I still get permanent residence?</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>إذا ما دفعت تأمين التقاعد، ما رح أقدر آخد الإقامة الدائمة؟</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>إذا لم أدفع اشتراكات تأمين التقاعد، هل لن أتمكن من الحصول على الإقامة الدائمة؟</t>
         </is>
       </c>
       <c r="F53" s="2" t="n"/>
-      <c r="G53" s="5" t="n"/>
+      <c r="G53" s="6" t="n"/>
       <c r="H53" s="2" t="n"/>
     </row>
     <row r="54">
@@ -2162,18 +2184,18 @@
           <t>Do foreign students also have to file a tax return? If so, what is the deadline?</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>الطلاب الأجانب كمان لازم يقدّموا تصريح ضريبي؟ وإذا لازم، لإيمتى آخر موعد؟</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>هل يجب على الطلاب الأجانب أيضاً تقديم إقرار ضريبي؟ وإذا كان كذلك، فما هو الموعد النهائي؟</t>
         </is>
       </c>
       <c r="F54" s="2" t="n"/>
-      <c r="G54" s="5" t="n"/>
+      <c r="G54" s="6" t="n"/>
       <c r="H54" s="2" t="n"/>
     </row>
     <row r="55">
@@ -2190,18 +2212,18 @@
           <t>🌍 I already have insurance in the Netherlands. Do I still have to take out health insurance in Germany?</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>عندي تأمين بهولندا أصلاً. لازم كمان اعمل تأمين صحي بألمانيا؟</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>لدي تأمين في هولندا بالفعل. هل يجب عليّ مع ذلك الاشتراك في تأمين صحي في ألمانيا؟</t>
         </is>
       </c>
       <c r="F55" s="2" t="n"/>
-      <c r="G55" s="5" t="n"/>
+      <c r="G55" s="6" t="n"/>
       <c r="H55" s="2" t="n"/>
     </row>
     <row r="56">
@@ -2218,18 +2240,18 @@
           <t>Is the Rundfunkbeitrag a tax? Do I have to pay it?</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>رسوم الـ GEZ هي ضريبة؟ ولازم ادفعها؟</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>هل رسوم الـ GEZ ضريبة؟ وهل يجب أن أدفعها؟</t>
         </is>
       </c>
       <c r="F56" s="2" t="n"/>
-      <c r="G56" s="5" t="n"/>
+      <c r="G56" s="6" t="n"/>
       <c r="H56" s="2" t="n"/>
     </row>
     <row r="57">
@@ -2246,18 +2268,18 @@
           <t>My salary is 50,000 euros a year. Exactly how much tax will I pay?</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>راتبي بالسنة 50,000 يورو. قديش بالزبط رح ادفع ضرايب؟</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>راتبي السنوي 50,000 يورو. كم ستكون الضريبة التي سأدفعها بالضبط؟</t>
         </is>
       </c>
       <c r="F57" s="2" t="n"/>
-      <c r="G57" s="5" t="n"/>
+      <c r="G57" s="6" t="n"/>
       <c r="H57" s="2" t="n"/>
     </row>
     <row r="58">
@@ -2274,18 +2296,18 @@
           <t>The tax office made a decision that seems wrong to me, and I want to object. Will I win?</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>مكتب الضرايب طلّع قرار شايفه غلط وبدي اعترض عليه. رح اربح؟</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>أصدرت مصلحة الضرائب قراراً يبدو لي خاطئاً وأريد الاعتراض عليه. هل سأربح؟</t>
         </is>
       </c>
       <c r="F58" s="2" t="n"/>
-      <c r="G58" s="5" t="n"/>
+      <c r="G58" s="6" t="n"/>
       <c r="H58" s="2" t="n"/>
     </row>
     <row r="59">
@@ -2302,18 +2324,18 @@
           <t>🌍 I'm Taiwanese and I'm here on a working holiday visa. I've been offered a permanent full-time job. Can I change my visa?</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>أنا تايواني وجاي بفيزا الـ Working Holiday. إجاني عرض شغل ثابت دوام كامل. فيني غيّر الفيزا؟</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>أنا تايواني وموجود هنا بتأشيرة عطلة العمل (Working Holiday). تلقيت عرض عمل ثابت بدوام كامل. هل يمكنني تغيير تأشيرتي؟</t>
         </is>
       </c>
       <c r="F59" s="2" t="n"/>
-      <c r="G59" s="5" t="n"/>
+      <c r="G59" s="6" t="n"/>
       <c r="H59" s="2" t="n"/>
     </row>
     <row r="60">
@@ -2330,18 +2352,18 @@
           <t>🌍 I'm Ukrainian. I worked for a German company for a year and was laid off. Can I get unemployment benefit?</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>أنا أوكراني، اشتغلت سنة بشركة ألمانية وبعدين طردوني. فيني آخد إعانة البطالة؟</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>أنا أوكراني، عملت لدى شركة ألمانية لمدة سنة ثم فُصلت من العمل. هل يمكنني الحصول على إعانة البطالة؟</t>
         </is>
       </c>
       <c r="F60" s="2" t="n"/>
-      <c r="G60" s="5" t="n"/>
+      <c r="G60" s="6" t="n"/>
       <c r="H60" s="2" t="n"/>
     </row>
     <row r="61">
@@ -2358,18 +2380,18 @@
           <t>🌍 I'm French and work in Germany. Can my American spouse live in Germany with me? Do they need a separate residence permit?</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>أنا فرنسي وبشتغل بألمانيا. مرتي أو جوزي أمريكاني، فيه يعيش معي بألمانيا؟ ولازم ياخد إقامة لحاله؟</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>أنا فرنسي وأعمل في ألمانيا. هل يمكن لزوجتي أو زوجي الأمريكي العيش معي في ألمانيا؟ وهل يحتاج إلى تصريح إقامة خاص؟</t>
         </is>
       </c>
       <c r="F61" s="2" t="n"/>
-      <c r="G61" s="5" t="n"/>
+      <c r="G61" s="6" t="n"/>
       <c r="H61" s="2" t="n"/>
     </row>
   </sheetData>
@@ -2399,34 +2421,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Term in the questions</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>German original (for you)</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>OK?</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>البطاقة الزرقاء</t>
         </is>
@@ -2438,7 +2460,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>أوسبيلدونغ</t>
         </is>
@@ -2450,7 +2472,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>الإقامة الدائمة</t>
         </is>
@@ -2462,7 +2484,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>دائرة الأجانب</t>
         </is>
@@ -2474,7 +2496,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>الوكالة الاتحادية للعمل</t>
         </is>
@@ -2486,7 +2508,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>بطاقة الفرص</t>
         </is>
@@ -2498,7 +2520,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>أوبير</t>
         </is>
@@ -2510,7 +2532,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>تسجيل السكن</t>
         </is>
@@ -2522,7 +2544,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>إقامة البحث عن شغل / عمل</t>
         </is>
@@ -2534,7 +2556,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Working Holiday</t>
         </is>
@@ -2546,7 +2568,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>التأمين الاجتماعي للفنانين</t>
         </is>
@@ -2558,7 +2580,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Werkstudent / HiWi</t>
         </is>
@@ -2570,7 +2592,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>الميني جوب</t>
         </is>
@@ -2582,7 +2604,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>الكيندرغيلد</t>
         </is>
@@ -2594,7 +2616,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>الرقم الضريبي</t>
         </is>
@@ -2606,7 +2628,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>رسوم الـ GEZ</t>
         </is>
@@ -2618,7 +2640,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>إلغاء تسجيل السكن</t>
         </is>
@@ -2630,7 +2652,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>إعانة البطالة</t>
         </is>
